--- a/output/graficos_regionales/plot_regional_serie_i_ingr_mean_s_2021_magallanes.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_mean_s_2021_magallanes.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:47</t>
+    <t xml:space="preserve">2026-10-05 02:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -505,7 +505,7 @@
         <v>384182.94</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>325846.62</v>
+        <v>325846.63</v>
       </c>
     </row>
     <row r="4">
@@ -634,7 +634,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>516543.12</v>
+        <v>516543.13</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>465428.69</v>
